--- a/data.xlsx
+++ b/data.xlsx
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes</t>
+          <t>Chemistry Med Easy | Notes, Formulas, Tips &amp; Tricks for NEET/JEE &amp; Board Exams | Pankaj Sir Chemistry Handwritten Notes!</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
